--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_HAPOEL IBI TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_HAPOEL IBI TEL AVIV.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3503</v>
+        <v>10.9435</v>
       </c>
       <c r="E2" t="n">
-        <v>12.9824</v>
+        <v>10.3514</v>
       </c>
       <c r="F2" t="n">
-        <v>1.367899999999999</v>
+        <v>0.5921000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>9.4277</v>
@@ -610,13 +610,13 @@
         <v>7.961500000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6252</v>
+        <v>0.2184</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6587</v>
+        <v>0.02779999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9663999999999998</v>
+        <v>0.1905999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-3.252</v>
@@ -643,13 +643,13 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4052</v>
+        <v>4.9127</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.037</v>
+        <v>-0.4263000000000003</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4421</v>
+        <v>5.3392</v>
       </c>
       <c r="G3" t="n">
         <v>4.896100000000001</v>
@@ -688,13 +688,13 @@
         <v>7.2792</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1267999999999999</v>
+        <v>0.6344000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2085</v>
+        <v>-0.5979</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3352</v>
+        <v>1.2323</v>
       </c>
       <c r="V3" t="n">
         <v>2.5668</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2747</v>
+        <v>0.9821</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2394</v>
+        <v>2.0793</v>
       </c>
       <c r="F4" t="n">
-        <v>2.035200000000001</v>
+        <v>-1.0972</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7650999999999999</v>
+        <v>4.983099999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.9469</v>
+        <v>-0.5725999999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1816</v>
+        <v>5.5558</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9955</v>
+        <v>9.055</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.732</v>
+        <v>3.3974</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7276</v>
+        <v>5.6577</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7607</v>
+        <v>-4.072</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2148</v>
+        <v>-3.9701</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.546</v>
+        <v>-0.102</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5021</v>
+        <v>-7.9616</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2747</v>
+        <v>-12.7385</v>
       </c>
       <c r="R4" t="n">
         <v>4.7769</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5595</v>
+        <v>-1.8768</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7298</v>
+        <v>-0.9363</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2894</v>
+        <v>-0.9406</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.0218</v>
+        <v>5.8373</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2485</v>
+        <v>6.699</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.2703</v>
+        <v>-0.8618000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2758</v>
+        <v>0.861</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2565999999999999</v>
+        <v>-0.6068</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5325</v>
+        <v>1.4678</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4776</v>
@@ -844,13 +844,13 @@
         <v>1.5923</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2084</v>
+        <v>-0.2065</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1555</v>
+        <v>-0.5058</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3638</v>
+        <v>0.2993</v>
       </c>
       <c r="V5" t="n">
         <v>1.0901</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PALATIN</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3725</v>
+        <v>0.6459000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0.2903</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3725</v>
+        <v>0.9362999999999997</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3725</v>
+        <v>-0.7650999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-2.9469</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3725</v>
+        <v>2.1816</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.9955</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.732</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.7276</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3725</v>
+        <v>-2.7607</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-2.2148</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3725</v>
+        <v>-0.546</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5021</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.2747</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4.7769</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.9307000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1.2597</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.1904</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.0218</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2485</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.2703</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. TIMOR</t>
+          <t>G. PALATIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,43 +952,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9675</v>
+        <v>-0.3725</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.05450000000000001</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9129</v>
+        <v>-0.3725</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9172</v>
+        <v>-0.3725</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3278</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5894</v>
+        <v>-0.3725</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0173</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0173</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9345</v>
+        <v>-0.3725</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3451</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5894</v>
+        <v>-0.3725</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0503</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0718</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0215</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>B. TIMOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1257</v>
+        <v>-0.9351</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7413999999999997</v>
+        <v>-0.05450000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.867099999999999</v>
+        <v>-0.8806</v>
       </c>
       <c r="G8" t="n">
-        <v>4.983099999999999</v>
+        <v>-0.9172</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5725999999999998</v>
+        <v>-0.3278</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5558</v>
+        <v>-0.5894</v>
       </c>
       <c r="J8" t="n">
-        <v>9.055</v>
+        <v>0.0173</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3974</v>
+        <v>0.0173</v>
       </c>
       <c r="L8" t="n">
-        <v>5.6577</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.072</v>
+        <v>-0.9345</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.9701</v>
+        <v>-0.3451</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.102</v>
+        <v>-0.5894</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.9616</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-12.7385</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.7769</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.9844</v>
+        <v>-0.018</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.2742</v>
+        <v>-0.0718</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.7103</v>
+        <v>0.0539</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8373</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>6.699</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8618000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.739</v>
+        <v>-2.5871</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7637999999999998</v>
+        <v>-4.137600000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9752</v>
+        <v>1.550600000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7808</v>
+        <v>-6.3847</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6559</v>
+        <v>-3.7026</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1249</v>
+        <v>-2.6822</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6955999999999998</v>
+        <v>-0.3000999999999996</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1780999999999999</v>
+        <v>-0.2332000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5175</v>
+        <v>-0.06699999999999995</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0852</v>
+        <v>-6.0846</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4778</v>
+        <v>-3.4694</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6074</v>
+        <v>-2.6152</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4549</v>
+        <v>0.6823999999999995</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3649</v>
+        <v>-6.8242</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9099</v>
+        <v>7.5066</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7518</v>
+        <v>0.1616000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0481</v>
+        <v>-0.987</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7999000000000001</v>
+        <v>1.1486</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2485</v>
+        <v>2.9536</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2485</v>
+        <v>3.9737</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0201</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9269</v>
+        <v>-3.6427</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.0592</v>
+        <v>-1.1141</v>
       </c>
       <c r="F10" t="n">
-        <v>2.132400000000001</v>
+        <v>-2.5286</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.3847</v>
+        <v>-3.7808</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7026</v>
+        <v>-1.6559</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6822</v>
+        <v>-2.1249</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3000999999999996</v>
+        <v>-0.6955999999999998</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2332000000000001</v>
+        <v>-0.1780999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.06699999999999995</v>
+        <v>-0.5175</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.0846</v>
+        <v>-3.0852</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.4694</v>
+        <v>-1.4778</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6152</v>
+        <v>-1.6074</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6823999999999995</v>
+        <v>-0.4549</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.8242</v>
+        <v>-1.3649</v>
       </c>
       <c r="R10" t="n">
-        <v>7.5066</v>
+        <v>0.9099</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1782</v>
+        <v>-0.6554</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.9086</v>
+        <v>-0.3021</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7304</v>
+        <v>-0.3534</v>
       </c>
       <c r="V10" t="n">
-        <v>2.9536</v>
+        <v>1.2485</v>
       </c>
       <c r="W10" t="n">
-        <v>3.9737</v>
+        <v>1.2485</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.672000000000001</v>
+        <v>-5.55</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.2593</v>
+        <v>-4.4927</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4128</v>
+        <v>-1.0572</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8348</v>
@@ -1312,13 +1312,13 @@
         <v>3.867</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1812</v>
+        <v>-2.0591</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6461</v>
+        <v>-0.8797</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5351</v>
+        <v>-1.1795</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2485</v>
@@ -1345,13 +1345,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7161</v>
+        <v>-6.0142</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9965</v>
+        <v>-3.23</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7197</v>
+        <v>-2.7842</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0618</v>
@@ -1390,13 +1390,13 @@
         <v>0.4549</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6633</v>
+        <v>0.3652</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2993999999999999</v>
+        <v>0.06599999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3638</v>
+        <v>0.2992</v>
       </c>
       <c r="V12" t="n">
         <v>-1.6352</v>
@@ -1423,13 +1423,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.4678</v>
+        <v>-7.0941</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.8741</v>
+        <v>-7.146700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5938000000000001</v>
+        <v>0.05259999999999987</v>
       </c>
       <c r="G13" t="n">
         <v>-5.8711</v>
@@ -1468,13 +1468,13 @@
         <v>4.0945</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.9571</v>
+        <v>-1.5834</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4003</v>
+        <v>-0.6728</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5569</v>
+        <v>-0.9104999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.1802</v>
@@ -1501,13 +1501,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.042400000000001</v>
+        <v>-8.322799999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.6224</v>
+        <v>-5.1554</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.42</v>
+        <v>-3.1674</v>
       </c>
       <c r="G14" t="n">
         <v>-4.6668</v>
@@ -1546,13 +1546,13 @@
         <v>1.5923</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.444</v>
+        <v>-0.7242999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3407</v>
+        <v>-0.8738</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1032</v>
+        <v>0.1495</v>
       </c>
       <c r="V14" t="n">
         <v>-2.0219</v>
@@ -1579,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.674</v>
+        <v>-10.01</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.4805</v>
+        <v>-5.779999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.1936</v>
+        <v>-4.229900000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-9.694700000000001</v>
@@ -1624,13 +1624,13 @@
         <v>5.2318</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.7351</v>
+        <v>-2.0711</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.424</v>
+        <v>-0.7237</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.3111</v>
+        <v>-1.3474</v>
       </c>
       <c r="V15" t="n">
         <v>-2.3385</v>
@@ -1657,13 +1657,13 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>-28.3979</v>
+        <v>-26.1833</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.4407</v>
+        <v>-20.0037</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.957499999999999</v>
+        <v>-6.178999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-21.5202</v>
@@ -1678,7 +1678,7 @@
         <v>13.8549</v>
       </c>
       <c r="K16" t="n">
-        <v>4.670300000000003</v>
+        <v>4.670299999999999</v>
       </c>
       <c r="L16" t="n">
         <v>9.184899999999999</v>
@@ -1693,7 +1693,7 @@
         <v>-16.4437</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.137599999999999</v>
+        <v>-1.1376</v>
       </c>
       <c r="Q16" t="n">
         <v>-51.1818</v>
@@ -1702,13 +1702,13 @@
         <v>50.0438</v>
       </c>
       <c r="S16" t="n">
-        <v>-9.0989</v>
+        <v>-6.884299999999998</v>
       </c>
       <c r="T16" t="n">
-        <v>-9.1533</v>
+        <v>-7.7168</v>
       </c>
       <c r="U16" t="n">
-        <v>0.05399999999999983</v>
+        <v>0.8324000000000003</v>
       </c>
       <c r="V16" t="n">
         <v>3.358599999999999</v>
